--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487681_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487681_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIAWARA</t>
+          <t>I. GARCIA GALLARDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7661</v>
+        <v>4.0539</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2285</v>
+        <v>-0.8014</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5376</v>
+        <v>4.8553</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8368</v>
+        <v>1.7572</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2002</v>
+        <v>-1.0389</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6366</v>
+        <v>2.7961</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8618</v>
+        <v>1.2253</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0093</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8525</v>
+        <v>2.0121</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.025</v>
+        <v>0.532</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8091</v>
+        <v>-0.2521</v>
       </c>
       <c r="O2" t="n">
         <v>0.7841</v>
       </c>
       <c r="P2" t="n">
-        <v>0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1344</v>
+        <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7353</v>
+        <v>0.5787</v>
       </c>
       <c r="T2" t="n">
-        <v>2.307</v>
+        <v>-0.3685</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4283</v>
+        <v>0.9472</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.9418</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. GARCIA GALLARDO</t>
+          <t>M. DIAWARA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3715</v>
+        <v>3.4738</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.402</v>
+        <v>0.4267</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7736</v>
+        <v>3.047</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7572</v>
+        <v>1.8368</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0389</v>
+        <v>0.2002</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7961</v>
+        <v>1.6366</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2253</v>
+        <v>1.8618</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7868000000000001</v>
+        <v>1.0093</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0121</v>
+        <v>0.8525</v>
       </c>
       <c r="M3" t="n">
-        <v>0.532</v>
+        <v>-0.025</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2521</v>
+        <v>-0.8091</v>
       </c>
       <c r="O3" t="n">
         <v>0.7841</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7164</v>
+        <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1036</v>
+        <v>1.4429</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9691</v>
+        <v>0.5052</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.9377</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9418</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8222</v>
+        <v>1.977</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6549</v>
+        <v>0.1805</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4772</v>
+        <v>1.7965</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0176</v>
+        <v>3.2707</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1824</v>
+        <v>-0.7028</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8351</v>
+        <v>3.9735</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4191</v>
+        <v>3.4407</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9732</v>
+        <v>0.2513</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4459</v>
+        <v>3.1894</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5985</v>
+        <v>-0.17</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2092</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3893</v>
+        <v>0.7841</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.5224</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.8508</v>
+        <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3284</v>
+        <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0132</v>
+        <v>0.0362</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7874</v>
+        <v>-0.6318</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7741</v>
+        <v>0.6679</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6597</v>
+        <v>-0.9418</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5642</v>
+        <v>0.2821</v>
       </c>
       <c r="X4" t="n">
         <v>-1.2239</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3036</v>
+        <v>1.9134</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5202</v>
+        <v>-0.4547</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8238</v>
+        <v>2.3681</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2707</v>
+        <v>5.0176</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7028</v>
+        <v>2.1824</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9735</v>
+        <v>2.8351</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4407</v>
+        <v>4.4191</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2513</v>
+        <v>1.9732</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1894</v>
+        <v>2.4459</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.17</v>
+        <v>0.5985</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9540999999999999</v>
+        <v>0.2092</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7841</v>
+        <v>0.3893</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3881</v>
+        <v>-2.5224</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-4.8508</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5224</v>
+        <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6373</v>
+        <v>0.078</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3325</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6952</v>
+        <v>0.6651</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9418</v>
+        <v>-0.6597</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2821</v>
+        <v>0.5642</v>
       </c>
       <c r="X5" t="n">
         <v>-1.2239</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1528</v>
+        <v>1.4621</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7202</v>
+        <v>0.9204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4326</v>
+        <v>0.5416</v>
       </c>
       <c r="G6" t="n">
         <v>0.8586</v>
@@ -922,13 +922,13 @@
         <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.764</v>
+        <v>-0.4548</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1584</v>
+        <v>-0.0493</v>
       </c>
       <c r="V6" t="n">
         <v>0.2821</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8762</v>
+        <v>-0.7216</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5401</v>
+        <v>-0.44</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3361</v>
+        <v>-0.2816</v>
       </c>
       <c r="G7" t="n">
         <v>0.4002</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4123</v>
+        <v>-0.2577</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2306</v>
+        <v>-0.1761</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2821</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0823</v>
+        <v>-1.2697</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0799</v>
+        <v>-1.0307</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0024</v>
+        <v>-0.239</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2376</v>
+        <v>-0.345</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3188</v>
+        <v>0.061</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.406</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5655</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3279</v>
+        <v>-0.345</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3279</v>
+        <v>0.061</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.406</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3881</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2732</v>
+        <v>-0.1486</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4856</v>
+        <v>-0.0606</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2124</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2665</v>
+        <v>-1.401</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1035</v>
+        <v>-0.4803</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.163</v>
+        <v>-0.9207</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2325</v>
+        <v>-0.2376</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8224</v>
+        <v>-0.3188</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5899</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4805</v>
+        <v>-0.5655</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3151</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8346</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2481</v>
+        <v>0.3279</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4927</v>
+        <v>0.3279</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2447</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7164</v>
+        <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8607</v>
+        <v>-0.0454</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1795</v>
+        <v>0.0852</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0402</v>
+        <v>-0.1307</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1657</v>
+        <v>-1.506</v>
       </c>
       <c r="W9" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.6716</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.297</v>
+        <v>-1.6847</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0307</v>
+        <v>-1.3037</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2663</v>
+        <v>-0.3811</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.345</v>
+        <v>0.2325</v>
       </c>
       <c r="H10" t="n">
-        <v>0.061</v>
+        <v>1.8224</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.406</v>
+        <v>-1.5899</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2.3151</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.8346</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.345</v>
+        <v>-0.2481</v>
       </c>
       <c r="N10" t="n">
-        <v>0.061</v>
+        <v>-0.4927</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.406</v>
+        <v>0.2447</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7761</v>
+        <v>-0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R10" t="n">
-        <v>0.194</v>
+        <v>2.7164</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1759</v>
+        <v>0.4425</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0606</v>
+        <v>-0.3797</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1153</v>
+        <v>0.8222</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.1657</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-3.6716</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1213</v>
+        <v>-2.0301</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.041</v>
+        <v>-2.4404</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0803</v>
+        <v>0.4103</v>
       </c>
       <c r="G11" t="n">
         <v>0.0573</v>
@@ -1312,13 +1312,13 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2488</v>
+        <v>-0.1576</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9085</v>
+        <v>-0.3079</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3403</v>
+        <v>0.1503</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3776</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.772899999999998</v>
+        <v>5.773099999999999</v>
       </c>
       <c r="E12" t="n">
         <v>-5.4236</v>
       </c>
       <c r="F12" t="n">
-        <v>11.1967</v>
+        <v>11.1964</v>
       </c>
       <c r="G12" t="n">
         <v>12.8483</v>
@@ -1390,13 +1390,13 @@
         <v>15.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5141</v>
+        <v>1.5142</v>
       </c>
       <c r="T12" t="n">
         <v>-2.2324</v>
       </c>
       <c r="U12" t="n">
-        <v>3.746199999999999</v>
+        <v>3.7463</v>
       </c>
       <c r="V12" t="n">
         <v>-4.709000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7214</v>
+        <v>2.3398</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0094</v>
+        <v>0.391</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7308</v>
+        <v>1.9489</v>
       </c>
       <c r="G13" t="n">
         <v>0.2793</v>
@@ -1468,13 +1468,13 @@
         <v>1.9403</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7519</v>
+        <v>-0.1335</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6662</v>
+        <v>-0.2658</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0857</v>
+        <v>0.1324</v>
       </c>
       <c r="V13" t="n">
         <v>1.2239</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>M. VILLAMANDOS TORRES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6597</v>
+        <v>0.7407</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1238</v>
+        <v>-0.25</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5358</v>
+        <v>0.9907</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4074</v>
+        <v>-2.8774</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6599</v>
+        <v>-2.3497</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.5278</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1206</v>
+        <v>-1.6743</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2018</v>
+        <v>-1.6971</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0228</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2867</v>
+        <v>-1.2031</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4581</v>
+        <v>-0.6525</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8286</v>
+        <v>-0.5506</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5523</v>
+        <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>1.467</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2445</v>
+        <v>-0.0533</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2226</v>
+        <v>0.1475</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0478</v>
+        <v>2.1657</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0478</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. VILLAMANDOS TORRES</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4776</v>
+        <v>0.514</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3506</v>
+        <v>-0.4768</v>
       </c>
       <c r="F15" t="n">
-        <v>1.127</v>
+        <v>0.9908</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.8774</v>
+        <v>-1.4074</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3497</v>
+        <v>-0.6599</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5278</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.6743</v>
+        <v>-0.1206</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.6971</v>
+        <v>-0.2018</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0228</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2031</v>
+        <v>-1.2867</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6525</v>
+        <v>-0.4581</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5506</v>
+        <v>-0.8286</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3284</v>
+        <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.3213</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5473</v>
+        <v>-0.3561</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2838</v>
+        <v>0.6775</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1657</v>
+        <v>0.0478</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2821</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0134</v>
+        <v>0.214</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5962</v>
+        <v>-0.396</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5828</v>
+        <v>0.61</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3454</v>
@@ -1702,13 +1702,13 @@
         <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3576</v>
+        <v>-0.1301</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5451</v>
+        <v>-0.3449</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1875</v>
+        <v>0.2148</v>
       </c>
       <c r="V16" t="n">
         <v>1.8836</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0184</v>
+        <v>-0.0095</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.051</v>
+        <v>-1.1511</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0326</v>
+        <v>1.1416</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3703</v>
@@ -1780,13 +1780,13 @@
         <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1579</v>
+        <v>0.1668</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1828</v>
+        <v>0.0827</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0249</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0312</v>
+        <v>-0.0129</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7418</v>
+        <v>-0.6417</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7106</v>
+        <v>0.6288</v>
       </c>
       <c r="G18" t="n">
         <v>0.2467</v>
@@ -1858,13 +1858,13 @@
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0063</v>
+        <v>0.0121</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.424</v>
+        <v>-0.3239</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4177</v>
+        <v>0.3359</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6597</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5213</v>
+        <v>-1.4668</v>
       </c>
       <c r="E19" t="n">
         <v>-1.5449</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0237</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>1.1947</v>
@@ -1936,13 +1936,13 @@
         <v>3.4926</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3876</v>
+        <v>-0.3331</v>
       </c>
       <c r="T19" t="n">
         <v>-0.6651</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2775</v>
+        <v>0.332</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3521</v>
+        <v>-2.3249</v>
       </c>
       <c r="E20" t="n">
         <v>-2.5985</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2464</v>
+        <v>0.2736</v>
       </c>
       <c r="G20" t="n">
         <v>-4.5284</v>
@@ -2014,13 +2014,13 @@
         <v>2.5224</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5998</v>
+        <v>-0.5726</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4229</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.177</v>
+        <v>-0.1497</v>
       </c>
       <c r="V20" t="n">
         <v>1.2239</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1088</v>
+        <v>-2.5177</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8674</v>
+        <v>-3.467</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.9494</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4595</v>
@@ -2092,13 +2092,13 @@
         <v>2.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0852</v>
+        <v>-0.4941</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1508</v>
+        <v>-0.7504</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0655</v>
+        <v>0.2563</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5642</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5863</v>
+        <v>-3.2498</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2617</v>
+        <v>-1.0615</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3246</v>
+        <v>-2.1884</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5807</v>
@@ -2170,13 +2170,13 @@
         <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7817</v>
+        <v>-0.4453</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8468</v>
+        <v>-0.6466</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.2014</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6119</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7728</v>
+        <v>-5.773100000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-11.1965</v>
       </c>
       <c r="F23" t="n">
-        <v>5.4237</v>
+        <v>5.423599999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-12.8484</v>
@@ -2248,16 +2248,16 @@
         <v>19.4033</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5141</v>
+        <v>-1.5143</v>
       </c>
       <c r="T23" t="n">
         <v>-3.7463</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2321</v>
+        <v>2.2322</v>
       </c>
       <c r="V23" t="n">
-        <v>4.709100000000001</v>
+        <v>4.709099999999999</v>
       </c>
       <c r="W23" t="n">
         <v>8.4717</v>
